--- a/Contenidos_Consultados/output/contenidos_consultados_febrero_2026.xlsx
+++ b/Contenidos_Consultados/output/contenidos_consultados_febrero_2026.xlsx
@@ -583,15 +583,15 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>1- SA06CUX03 Confirmar turno Sí, dale: (373.253)
-2- TUR00CUX02 Turnos para salud: (133.598)
-3- Infracciones * Apertura: (125.263)
-4- edu06push02_comienzoclases_primaria: (112.642)
+2- miBA - Login exitoso: (144.056)
+3- TUR00CUX02 Turnos para salud: (133.598)
+4- Infracciones * Apertura: (125.263)
 5- SA06CUX02 Apertura: (100.459)
 6- MO00CUX01 Auto o moto: (95.631)
-7- miba01push01_codigo_autenticacion: (90.210)
-8- SA10CUX01 Hospitales: (75.067)
-9- MO05CUX02 Apertura: (72.302)
-10- edu10push02_inscripcionadultos_2026_v2: (70.039)</t>
+7- SA10CUX01 Hospitales: (75.067)
+8- MO05CUX02 Apertura: (72.302)
+9- TR00CUX01 Apertura: (62.913)
+10- Licencia prorroga  &gt; Consultar: (62.240)</t>
         </is>
       </c>
     </row>

--- a/Contenidos_Consultados/output/contenidos_consultados_febrero_2026.xlsx
+++ b/Contenidos_Consultados/output/contenidos_consultados_febrero_2026.xlsx
@@ -582,16 +582,16 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1- SA06CUX03 Confirmar turno Sí, dale: (373.253)
-2- miBA - Login exitoso: (144.056)
-3- TUR00CUX02 Turnos para salud: (133.598)
-4- Infracciones * Apertura: (125.263)
-5- SA06CUX02 Apertura: (100.459)
-6- MO00CUX01 Auto o moto: (95.631)
-7- SA10CUX01 Hospitales: (75.067)
-8- MO05CUX02 Apertura: (72.302)
-9- TR00CUX01 Apertura: (62.913)
-10- Licencia prorroga  &gt; Consultar: (62.240)</t>
+          <t>1- Confirmación Turnos Salud: (373.253)
+2- Turnos Salud: (133.598)
+3- Infracciones: (125.263)
+4- Mis profesionales: (100.459)
+5- Trámites Vehículos SAP: (95.631)
+6- Hospitales: (75.067)
+7- Licencias: (72.302)
+8- Trámites SAP: (62.913)
+9- Buscar donde está permitido estacionar: (47.309)
+10- SA17CUX01 Apertura : (26.026)</t>
         </is>
       </c>
     </row>
